--- a/data/trans_bre/P71_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 14,05</t>
+          <t>6,39; 14,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -0,12</t>
+          <t>-8,65; -0,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 7,19</t>
+          <t>-2,23; 7,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,09</t>
+          <t>-4,32; 5,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 50,8</t>
+          <t>19,7; 49,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,54; -0,44</t>
+          <t>-20,06; -1,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 15,84</t>
+          <t>-4,42; 15,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 21,01</t>
+          <t>-14,76; 21,27</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,8</t>
+          <t>5,11; 11,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,46</t>
+          <t>-0,71; 5,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,21</t>
+          <t>-2,43; 3,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 14,42</t>
+          <t>0,6; 15,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,0; 81,6</t>
+          <t>31,93; 82,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 19,09</t>
+          <t>-2,3; 19,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 9,7</t>
+          <t>-6,71; 11,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 143,21</t>
+          <t>5,99; 151,97</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 9,09</t>
+          <t>1,48; 8,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 7,49</t>
+          <t>-1,83; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 7,45</t>
+          <t>-0,98; 7,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,69</t>
+          <t>0,4; 4,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 167,09</t>
+          <t>15,82; 161,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 73,92</t>
+          <t>-14,88; 76,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 87,26</t>
+          <t>-8,36; 82,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 252,59</t>
+          <t>8,25; 271,56</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,97</t>
+          <t>7,68; 11,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,17</t>
+          <t>-1,24; 3,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,64</t>
+          <t>-0,1; 4,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 11,65</t>
+          <t>1,64; 10,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,78; 69,44</t>
+          <t>40,33; 69,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 10,69</t>
+          <t>-3,88; 10,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 14,24</t>
+          <t>-0,13; 14,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,85; 98,33</t>
+          <t>11,91; 94,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P71_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>-2,89%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 14,08</t>
+          <t>6,33; 14,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; -0,43</t>
+          <t>-8,19; -0,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 7,19</t>
+          <t>-2,43; 7,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 5,05</t>
+          <t>-5,47; 4,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,7; 49,35</t>
+          <t>20,04; 53,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,06; -1,05</t>
+          <t>-18,92; -0,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 15,94</t>
+          <t>-4,79; 15,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 21,27</t>
+          <t>-17,02; 16,07</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,03</t>
+          <t>4,93; 10,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 5,59</t>
+          <t>-0,6; 5,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,6</t>
+          <t>-2,59; 3,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 15,45</t>
+          <t>0,06; 4,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,93; 82,82</t>
+          <t>31,71; 79,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 19,21</t>
+          <t>-1,9; 20,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 11,22</t>
+          <t>-7,24; 10,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 151,97</t>
+          <t>0,32; 35,75</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,98</t>
+          <t>1,72; 9,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 7,44</t>
+          <t>-2,23; 7,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 7,57</t>
+          <t>-0,95; 7,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,59</t>
+          <t>0,26; 4,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,82; 161,94</t>
+          <t>17,73; 172,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 76,61</t>
+          <t>-15,63; 72,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 82,71</t>
+          <t>-6,37; 81,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,25; 271,56</t>
+          <t>1,33; 223,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,9</t>
+          <t>7,74; 11,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,14</t>
+          <t>-1,24; 3,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 4,71</t>
+          <t>-0,05; 4,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,69</t>
+          <t>0,7; 4,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,33; 69,85</t>
+          <t>41,09; 70,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 10,64</t>
+          <t>-3,94; 10,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 14,64</t>
+          <t>-0,28; 14,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 94,22</t>
+          <t>4,83; 32,33</t>
         </is>
       </c>
     </row>
